--- a/output/pdf_financials_xlsx/ANON.xlsx
+++ b/output/pdf_financials_xlsx/ANON.xlsx
@@ -2063,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.591632</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.669579</v>
       </c>
     </row>
     <row r="93">
@@ -3242,7 +3242,11 @@
           <t>Reserves 9, 10, 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ANON.xlsx
+++ b/output/pdf_financials_xlsx/ANON.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.133735</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.233072</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.705396</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.133735</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.233072</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.705396</v>
       </c>
     </row>
     <row r="37">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.201278</v>
+        <v>0.06754300000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.282806</v>
+        <v>0.049734</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.752615</v>
+        <v>0.047219</v>
       </c>
     </row>
     <row r="49">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ANON.xlsx
+++ b/output/pdf_financials_xlsx/ANON.xlsx
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.079254</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.2416</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.124615</v>
       </c>
     </row>
     <row r="65">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.15197</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.141394</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.089368</v>
       </c>
     </row>
     <row r="68">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.02028</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010292</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.001585</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -3827,7 +3827,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.02028</v>
       </c>
@@ -4319,7 +4323,11 @@
           <t>Accrued interest and accretion expense</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.001585</v>
       </c>
